--- a/data/trans_orig/IP07C14-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C14-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>23762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17823</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16621</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28778</t>
+          <t>29076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25926</t>
+          <t>26306</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>10807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>16084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24074</t>
+          <t>23738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>12890</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19515</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16163</t>
+          <t>16731</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28573</t>
+          <t>29283</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>22207</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27357</t>
+          <t>26651</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16111</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21866</t>
+          <t>22384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37908</t>
+          <t>38023</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26073</t>
+          <t>25945</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>13646</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21295</t>
+          <t>20490</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36688</t>
+          <t>36285</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>36299</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19811</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33178</t>
+          <t>33042</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44885</t>
+          <t>46303</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64807</t>
+          <t>66512</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22596</t>
+          <t>22489</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>15401</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>28686</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>18722</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27283</t>
+          <t>27653</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25813</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42955</t>
+          <t>42205</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>25974</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13256</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22407</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23771</t>
+          <t>24264</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26298</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42064</t>
+          <t>42193</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10006</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>22601</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>13782</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>13195</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24759</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>19842</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>34893</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>13514</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>18093</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13648</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13830</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12498</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>23887</t>
+          <t>23825</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>12817</t>
+          <t>13011</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>24975</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>49497</t>
+          <t>48505</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>70026</t>
+          <t>70275</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>49476</t>
+          <t>48743</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>84560</t>
+          <t>84797</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>113795</t>
+          <t>114461</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>39662</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>61115</t>
+          <t>61501</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>35566</t>
+          <t>36223</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>55727</t>
+          <t>55615</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>81067</t>
+          <t>81330</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>110850</t>
+          <t>110002</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>74188</t>
+          <t>73998</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>97815</t>
+          <t>99030</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>74579</t>
+          <t>74873</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>99574</t>
+          <t>99748</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>154160</t>
+          <t>155697</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>189272</t>
+          <t>190710</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>20071</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>36059</t>
+          <t>36207</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>34999</t>
+          <t>36696</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>54877</t>
+          <t>55513</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>60164</t>
+          <t>60939</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>85998</t>
+          <t>85865</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>34831</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>54545</t>
+          <t>53982</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>62180</t>
+          <t>62726</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>88626</t>
+          <t>84930</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>103701</t>
+          <t>103307</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>134017</t>
+          <t>134892</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>12182</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21653</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>30034</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9578</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12511</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12761</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22264</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23591</t>
+          <t>23186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>13340</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>10138</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20712</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>787</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>21718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>13699</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10741</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22358</t>
+          <t>21729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>15011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13662</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>26337</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>17427</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>27945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24936</t>
+          <t>25888</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>42356</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>22401</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19903</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>39027</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>17022</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30662</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25531</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40731</t>
+          <t>41224</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45672</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66575</t>
+          <t>67178</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17124</t>
+          <t>18191</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25066</t>
+          <t>23994</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21233</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38120</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19006</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>28967</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27168</t>
+          <t>26331</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44229</t>
+          <t>44279</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25398</t>
+          <t>25298</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>15396</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36956</t>
+          <t>37173</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22264</t>
+          <t>22171</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17348</t>
+          <t>17639</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20922</t>
+          <t>19660</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28081</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25198</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31085</t>
+          <t>30836</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>48890</t>
+          <t>48235</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14083</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>17956</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>28135</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25398</t>
+          <t>24742</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21936</t>
+          <t>21761</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>38318</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,3%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13653</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14620</t>
+          <t>15081</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>22142</t>
+          <t>22223</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18308</t>
+          <t>18438</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>60391</t>
+          <t>60302</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>84804</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>44256</t>
+          <t>45041</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>65573</t>
+          <t>65578</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>111704</t>
+          <t>110650</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>144050</t>
+          <t>144226</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>50062</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>71775</t>
+          <t>71624</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>33195</t>
+          <t>32890</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>51795</t>
+          <t>52346</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>86874</t>
+          <t>87093</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>116946</t>
+          <t>116878</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>66524</t>
+          <t>66844</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>92447</t>
+          <t>92109</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>78142</t>
+          <t>78621</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>103937</t>
+          <t>104024</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>150931</t>
+          <t>149984</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>187835</t>
+          <t>186161</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>29033</t>
+          <t>29153</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>48427</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>43198</t>
+          <t>42783</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>63893</t>
+          <t>65241</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>77317</t>
+          <t>78250</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>106709</t>
+          <t>107266</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>37381</t>
+          <t>37103</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>58050</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>52933</t>
+          <t>53614</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>77189</t>
+          <t>76766</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>96250</t>
+          <t>96590</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>128137</t>
+          <t>128156</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2016 (tasa de respuesta: 95,57%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2016 (tasa de respuesta: 95,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12515</t>
+          <t>12255</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17556</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13261</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12816</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19450</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11746</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24931</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>15169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18643</t>
+          <t>18242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>16023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30389</t>
+          <t>29532</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19469</t>
+          <t>19577</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17766</t>
+          <t>17993</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31299</t>
+          <t>32262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>14260</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15674</t>
+          <t>15496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13099</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26285</t>
+          <t>25412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>17181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11787</t>
+          <t>11590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20966</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17035</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26961</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>21417</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36099</t>
+          <t>37192</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25824</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37069</t>
+          <t>36375</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57741</t>
+          <t>55677</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26965</t>
+          <t>25816</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21182</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25304</t>
+          <t>25269</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43589</t>
+          <t>42739</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17400</t>
+          <t>17525</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31255</t>
+          <t>32183</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>16860</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31738</t>
+          <t>31502</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36763</t>
+          <t>37778</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56897</t>
+          <t>56474</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21107</t>
+          <t>21506</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13170</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27501</t>
+          <t>27458</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44576</t>
+          <t>44566</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33611</t>
+          <t>33105</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29171</t>
+          <t>29503</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38248</t>
+          <t>38064</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58529</t>
+          <t>58710</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20665</t>
+          <t>20517</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33329</t>
+          <t>33850</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14210</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15453</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29820</t>
+          <t>30985</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29823</t>
+          <t>29183</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>20585</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>29682</t>
+          <t>29365</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47239</t>
+          <t>46907</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>13293</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>26336</t>
+          <t>25909</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23943</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>41162</t>
+          <t>40283</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>36172</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>18850</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>8639</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14506</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29682</t>
+          <t>29307</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12932</t>
+          <t>14231</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>20796</t>
+          <t>20788</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>60298</t>
+          <t>59828</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>85058</t>
+          <t>84947</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>39317</t>
+          <t>39182</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>60450</t>
+          <t>60881</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>106157</t>
+          <t>106645</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>139368</t>
+          <t>140916</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>43523</t>
+          <t>43803</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>68257</t>
+          <t>66480</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>52999</t>
+          <t>52957</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>76580</t>
+          <t>77101</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>102524</t>
+          <t>103940</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>135183</t>
+          <t>136643</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>74644</t>
+          <t>74692</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>101719</t>
+          <t>101026</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>57017</t>
+          <t>57572</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>81988</t>
+          <t>82690</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>139769</t>
+          <t>138428</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>175171</t>
+          <t>174031</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>36650</t>
+          <t>36393</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>56796</t>
+          <t>56735</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>60554</t>
+          <t>58882</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>84458</t>
+          <t>83598</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>99391</t>
+          <t>101252</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>134177</t>
+          <t>133371</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>55092</t>
+          <t>55519</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>78272</t>
+          <t>78822</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>66615</t>
+          <t>66278</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>91218</t>
+          <t>91010</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>126019</t>
+          <t>127360</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>160728</t>
+          <t>162173</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
